--- a/Python/stringManipulation.xlsx
+++ b/Python/stringManipulation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\PythonBatch14\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EEB7064-2EC5-49B9-AD8B-333AFCF1C545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A79334-7EAE-42F5-B8F8-2F282AF16528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8B3DDA62-1547-41A7-977A-C3298BCF390F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>H</t>
   </si>
@@ -70,6 +70,24 @@
   </si>
   <si>
     <t>Right -&gt; Left</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -421,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551EF44D-B8CB-47CD-AF92-F059A769EB93}">
-  <dimension ref="B6:R13"/>
+  <dimension ref="B6:S18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="6" spans="2:18" x14ac:dyDescent="0.35">
@@ -587,6 +605,112 @@
         <v>14</v>
       </c>
     </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17">
+        <v>9</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17">
+        <v>11</v>
+      </c>
+      <c r="O17">
+        <v>12</v>
+      </c>
+      <c r="P17">
+        <v>13</v>
+      </c>
+      <c r="Q17">
+        <v>14</v>
+      </c>
+      <c r="R17">
+        <v>15</v>
+      </c>
+      <c r="S17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
